--- a/productos/04-control-inventario/Control-de-Inventario.xlsx
+++ b/productos/04-control-inventario/Control-de-Inventario.xlsx
@@ -130,7 +130,7 @@
     <t xml:space="preserve">8. Celdas protegidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Contraseña de desprotección: plantilla2026.</t>
+    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Si necesitas editar otra celda, ve a Revisar → Desproteger hoja (no pide contraseña).</t>
   </si>
   <si>
     <t xml:space="preserve">Soporte y otras plantillas de esta línea de productos: www.tumarca.com</t>
@@ -1494,11 +1494,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52067364"/>
-        <c:axId val="97861773"/>
+        <c:axId val="1611788"/>
+        <c:axId val="7759547"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52067364"/>
+        <c:axId val="1611788"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1530,7 +1530,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97861773"/>
+        <c:crossAx val="7759547"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1538,7 +1538,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97861773"/>
+        <c:axId val="7759547"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1580,7 +1580,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52067364"/>
+        <c:crossAx val="1611788"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1820,11 +1820,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="88853571"/>
-        <c:axId val="11460317"/>
+        <c:axId val="41315740"/>
+        <c:axId val="98330688"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="88853571"/>
+        <c:axId val="41315740"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1856,7 +1856,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11460317"/>
+        <c:crossAx val="98330688"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1864,7 +1864,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11460317"/>
+        <c:axId val="98330688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1906,7 +1906,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88853571"/>
+        <c:crossAx val="41315740"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2408,7 +2408,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:F6"/>
@@ -2559,7 +2559,7 @@
       <c r="C28" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="18">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
@@ -2706,7 +2706,7 @@
       <c r="D13" s="20"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B13:D13"/>
@@ -2830,7 +2830,7 @@
       <c r="C16" s="22"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B12:C12"/>
@@ -3160,7 +3160,7 @@
       <c r="H16" s="25"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
@@ -5605,7 +5605,7 @@
       <c r="F204" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
@@ -6210,7 +6210,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -6313,7 +6313,7 @@
       <c r="I7" s="46"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="10">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
